--- a/1_Input/Data_20251119.xlsx
+++ b/1_Input/Data_20251119.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RYAN.CHUANG\Desktop\Programming project\9_Fan System\1_Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CBB4581-09E2-448B-9819-248C6C9CAE1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55509857-35CF-48E7-8077-6DD2A551A3A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{979E5DA7-38E7-4466-9366-DBC429F4354F}"/>
   </bookViews>
@@ -859,7 +859,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -914,6 +914,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -929,7 +935,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1005,11 +1011,17 @@
     <xf numFmtId="176" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3801,26 +3813,26 @@
       <c r="X1" t="s">
         <v>204</v>
       </c>
-      <c r="Y1" s="26" t="s">
+      <c r="Y1" s="25" t="s">
         <v>205</v>
       </c>
-      <c r="Z1" s="26"/>
-      <c r="AA1" s="26" t="s">
+      <c r="Z1" s="25"/>
+      <c r="AA1" s="25" t="s">
         <v>206</v>
       </c>
-      <c r="AB1" s="26"/>
-      <c r="AC1" s="26" t="s">
+      <c r="AB1" s="25"/>
+      <c r="AC1" s="25" t="s">
         <v>207</v>
       </c>
-      <c r="AD1" s="26"/>
-      <c r="AE1" s="26" t="s">
+      <c r="AD1" s="25"/>
+      <c r="AE1" s="25" t="s">
         <v>208</v>
       </c>
-      <c r="AF1" s="26"/>
-      <c r="AG1" s="26" t="s">
+      <c r="AF1" s="25"/>
+      <c r="AG1" s="25" t="s">
         <v>209</v>
       </c>
-      <c r="AH1" s="26"/>
+      <c r="AH1" s="25"/>
     </row>
     <row r="2" spans="1:34" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
@@ -3895,26 +3907,26 @@
       <c r="X2" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="Y2" s="25" t="s">
+      <c r="Y2" s="26" t="s">
         <v>175</v>
       </c>
-      <c r="Z2" s="25"/>
-      <c r="AA2" s="25" t="s">
+      <c r="Z2" s="26"/>
+      <c r="AA2" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="AB2" s="25"/>
-      <c r="AC2" s="25" t="s">
+      <c r="AB2" s="26"/>
+      <c r="AC2" s="26" t="s">
         <v>177</v>
       </c>
-      <c r="AD2" s="25"/>
-      <c r="AE2" s="25" t="s">
+      <c r="AD2" s="26"/>
+      <c r="AE2" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="AF2" s="25"/>
-      <c r="AG2" s="25" t="s">
+      <c r="AF2" s="26"/>
+      <c r="AG2" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="AH2" s="25"/>
+      <c r="AH2" s="26"/>
     </row>
     <row r="3" spans="1:34" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -4868,427 +4880,427 @@
         <v>12.59928315</v>
       </c>
     </row>
-    <row r="12" spans="1:34" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="23" t="s">
+    <row r="12" spans="1:34" s="27" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="B12" s="23">
+      <c r="B12" s="27">
         <v>7000</v>
       </c>
-      <c r="C12" s="23">
+      <c r="C12" s="27">
         <v>47</v>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="27">
         <v>20.5</v>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="27">
         <v>15</v>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="27">
         <v>10.15</v>
       </c>
-      <c r="G12" s="23">
+      <c r="G12" s="27">
         <v>5</v>
       </c>
-      <c r="H12" s="23">
+      <c r="H12" s="27">
         <v>0.35</v>
       </c>
-      <c r="I12" s="23">
+      <c r="I12" s="27">
         <v>51.7</v>
       </c>
-      <c r="J12" s="23">
+      <c r="J12" s="27">
         <v>34.200000000000003</v>
       </c>
-      <c r="K12" s="23">
+      <c r="K12" s="27">
         <v>10.933050890000001</v>
       </c>
-      <c r="L12" s="23">
+      <c r="L12" s="27">
         <f t="shared" si="0"/>
         <v>8.5799999963076932</v>
       </c>
-      <c r="M12" s="23">
+      <c r="M12" s="27">
         <v>18.004446309999999</v>
       </c>
-      <c r="N12" s="23">
+      <c r="N12" s="27">
         <f t="shared" si="1"/>
         <v>10.119999998282127</v>
       </c>
-      <c r="O12" s="23">
-        <v>0</v>
-      </c>
-      <c r="P12" s="23">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="23">
+      <c r="O12" s="27">
+        <v>0</v>
+      </c>
+      <c r="P12" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="27">
         <v>1.2</v>
       </c>
-      <c r="R12" s="23">
+      <c r="R12" s="27">
         <v>0.6</v>
       </c>
-      <c r="S12" s="23">
+      <c r="S12" s="27">
         <v>0.05</v>
       </c>
-      <c r="T12" s="23">
+      <c r="T12" s="27">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="U12" s="23">
+      <c r="U12" s="27">
         <v>0.59</v>
       </c>
-      <c r="V12" s="23">
+      <c r="V12" s="27">
         <v>0.54</v>
       </c>
-      <c r="W12" s="23">
+      <c r="W12" s="27">
         <v>30</v>
       </c>
-      <c r="X12" s="23">
+      <c r="X12" s="27">
         <v>10</v>
       </c>
-      <c r="Y12" s="24">
+      <c r="Y12" s="28">
         <v>10.195098809999999</v>
       </c>
-      <c r="Z12" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="24">
+      <c r="Z12" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="28">
         <v>5.1329300919999996</v>
       </c>
-      <c r="AB12" s="24">
+      <c r="AB12" s="28">
         <v>8.9002468970000006</v>
       </c>
-      <c r="AC12" s="24">
+      <c r="AC12" s="28">
         <v>3.637645048</v>
       </c>
-      <c r="AD12" s="24">
+      <c r="AD12" s="28">
         <v>16.91610678</v>
       </c>
-      <c r="AE12" s="24">
+      <c r="AE12" s="28">
         <v>2.749885146</v>
       </c>
-      <c r="AF12" s="24">
+      <c r="AF12" s="28">
         <v>19.15248149</v>
       </c>
-      <c r="AG12" s="24">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="24">
+      <c r="AG12" s="28">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="28">
         <v>22.951750130000001</v>
       </c>
     </row>
-    <row r="13" spans="1:34" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="23" t="s">
+    <row r="13" spans="1:34" s="27" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="B13" s="23">
+      <c r="B13" s="27">
         <v>6000</v>
       </c>
-      <c r="C13" s="23">
+      <c r="C13" s="27">
         <v>47</v>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="27">
         <v>20.5</v>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="27">
         <v>15</v>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="27">
         <v>10.15</v>
       </c>
-      <c r="G13" s="23">
+      <c r="G13" s="27">
         <v>5</v>
       </c>
-      <c r="H13" s="23">
+      <c r="H13" s="27">
         <v>0.35</v>
       </c>
-      <c r="I13" s="23">
+      <c r="I13" s="27">
         <v>51.7</v>
       </c>
-      <c r="J13" s="23">
+      <c r="J13" s="27">
         <v>34.200000000000003</v>
       </c>
-      <c r="K13" s="23">
+      <c r="K13" s="27">
         <v>10.933050890000001</v>
       </c>
-      <c r="L13" s="23">
+      <c r="L13" s="27">
         <f t="shared" si="0"/>
         <v>8.5799999963076932</v>
       </c>
-      <c r="M13" s="23">
+      <c r="M13" s="27">
         <v>18.004446309999999</v>
       </c>
-      <c r="N13" s="23">
+      <c r="N13" s="27">
         <f t="shared" si="1"/>
         <v>10.119999998282127</v>
       </c>
-      <c r="O13" s="23">
-        <v>0</v>
-      </c>
-      <c r="P13" s="23">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="23">
+      <c r="O13" s="27">
+        <v>0</v>
+      </c>
+      <c r="P13" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="27">
         <v>1.2</v>
       </c>
-      <c r="R13" s="23">
+      <c r="R13" s="27">
         <v>0.6</v>
       </c>
-      <c r="S13" s="23">
+      <c r="S13" s="27">
         <v>0.05</v>
       </c>
-      <c r="T13" s="23">
+      <c r="T13" s="27">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="U13" s="23">
+      <c r="U13" s="27">
         <v>0.59</v>
       </c>
-      <c r="V13" s="23">
+      <c r="V13" s="27">
         <v>0.54</v>
       </c>
-      <c r="W13" s="23">
+      <c r="W13" s="27">
         <v>30</v>
       </c>
-      <c r="X13" s="23">
+      <c r="X13" s="27">
         <v>10</v>
       </c>
-      <c r="Y13" s="24">
+      <c r="Y13" s="28">
         <v>7.4902766789999999</v>
       </c>
-      <c r="Z13" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="24">
+      <c r="Z13" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="28">
         <v>3.7711323129999998</v>
       </c>
-      <c r="AB13" s="24">
+      <c r="AB13" s="28">
         <v>7.6287830550000004</v>
       </c>
-      <c r="AC13" s="24">
+      <c r="AC13" s="28">
         <v>2.6725555449999998</v>
       </c>
-      <c r="AD13" s="24">
+      <c r="AD13" s="28">
         <v>14.499520090000001</v>
       </c>
-      <c r="AE13" s="24">
+      <c r="AE13" s="28">
         <v>2.0203237810000001</v>
       </c>
-      <c r="AF13" s="24">
+      <c r="AF13" s="28">
         <v>16.416412699999999</v>
       </c>
-      <c r="AG13" s="24">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="24">
+      <c r="AG13" s="28">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="28">
         <v>19.672928689999999</v>
       </c>
     </row>
-    <row r="14" spans="1:34" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="23" t="s">
+    <row r="14" spans="1:34" s="27" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B14" s="27">
         <v>5000</v>
       </c>
-      <c r="C14" s="23">
+      <c r="C14" s="27">
         <v>47</v>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="27">
         <v>20.5</v>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="27">
         <v>15</v>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="27">
         <v>10.15</v>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="27">
         <v>5</v>
       </c>
-      <c r="H14" s="23">
+      <c r="H14" s="27">
         <v>0.35</v>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="27">
         <v>51.7</v>
       </c>
-      <c r="J14" s="23">
+      <c r="J14" s="27">
         <v>34.200000000000003</v>
       </c>
-      <c r="K14" s="23">
+      <c r="K14" s="27">
         <v>10.933050890000001</v>
       </c>
-      <c r="L14" s="23">
+      <c r="L14" s="27">
         <f t="shared" si="0"/>
         <v>8.5799999963076932</v>
       </c>
-      <c r="M14" s="23">
+      <c r="M14" s="27">
         <v>18.004446309999999</v>
       </c>
-      <c r="N14" s="23">
+      <c r="N14" s="27">
         <f t="shared" si="1"/>
         <v>10.119999998282127</v>
       </c>
-      <c r="O14" s="23">
-        <v>0</v>
-      </c>
-      <c r="P14" s="23">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="23">
+      <c r="O14" s="27">
+        <v>0</v>
+      </c>
+      <c r="P14" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="27">
         <v>1.2</v>
       </c>
-      <c r="R14" s="23">
+      <c r="R14" s="27">
         <v>0.6</v>
       </c>
-      <c r="S14" s="23">
+      <c r="S14" s="27">
         <v>0.05</v>
       </c>
-      <c r="T14" s="23">
+      <c r="T14" s="27">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="U14" s="23">
+      <c r="U14" s="27">
         <v>0.59</v>
       </c>
-      <c r="V14" s="23">
+      <c r="V14" s="27">
         <v>0.54</v>
       </c>
-      <c r="W14" s="23">
+      <c r="W14" s="27">
         <v>30</v>
       </c>
-      <c r="X14" s="23">
+      <c r="X14" s="27">
         <v>10</v>
       </c>
-      <c r="Y14" s="24">
+      <c r="Y14" s="28">
         <v>5.2015810269999996</v>
       </c>
-      <c r="Z14" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="24">
+      <c r="Z14" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="28">
         <v>2.6188418840000001</v>
       </c>
-      <c r="AB14" s="24">
+      <c r="AB14" s="28">
         <v>6.3573192120000002</v>
       </c>
-      <c r="AC14" s="24">
+      <c r="AC14" s="28">
         <v>1.855941351</v>
       </c>
-      <c r="AD14" s="24">
+      <c r="AD14" s="28">
         <v>12.082933410000001</v>
       </c>
-      <c r="AE14" s="24">
+      <c r="AE14" s="28">
         <v>1.4030026259999999</v>
       </c>
-      <c r="AF14" s="24">
+      <c r="AF14" s="28">
         <v>13.68034392</v>
       </c>
-      <c r="AG14" s="24">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="24">
+      <c r="AG14" s="28">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="28">
         <v>16.39410724</v>
       </c>
     </row>
-    <row r="15" spans="1:34" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="23" t="s">
+    <row r="15" spans="1:34" s="27" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B15" s="27">
         <v>4000</v>
       </c>
-      <c r="C15" s="23">
+      <c r="C15" s="27">
         <v>47</v>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="27">
         <v>20.5</v>
       </c>
-      <c r="E15" s="23">
+      <c r="E15" s="27">
         <v>15</v>
       </c>
-      <c r="F15" s="23">
+      <c r="F15" s="27">
         <v>10.15</v>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="27">
         <v>5</v>
       </c>
-      <c r="H15" s="23">
+      <c r="H15" s="27">
         <v>0.35</v>
       </c>
-      <c r="I15" s="23">
+      <c r="I15" s="27">
         <v>51.7</v>
       </c>
-      <c r="J15" s="23">
+      <c r="J15" s="27">
         <v>34.200000000000003</v>
       </c>
-      <c r="K15" s="23">
+      <c r="K15" s="27">
         <v>10.933050890000001</v>
       </c>
-      <c r="L15" s="23">
+      <c r="L15" s="27">
         <f t="shared" si="0"/>
         <v>8.5799999963076932</v>
       </c>
-      <c r="M15" s="23">
+      <c r="M15" s="27">
         <v>18.004446309999999</v>
       </c>
-      <c r="N15" s="23">
+      <c r="N15" s="27">
         <f t="shared" si="1"/>
         <v>10.119999998282127</v>
       </c>
-      <c r="O15" s="23">
-        <v>0</v>
-      </c>
-      <c r="P15" s="23">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="23">
+      <c r="O15" s="27">
+        <v>0</v>
+      </c>
+      <c r="P15" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="27">
         <v>1.2</v>
       </c>
-      <c r="R15" s="23">
+      <c r="R15" s="27">
         <v>0.6</v>
       </c>
-      <c r="S15" s="23">
+      <c r="S15" s="27">
         <v>0.05</v>
       </c>
-      <c r="T15" s="23">
+      <c r="T15" s="27">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="U15" s="23">
+      <c r="U15" s="27">
         <v>0.59</v>
       </c>
-      <c r="V15" s="23">
+      <c r="V15" s="27">
         <v>0.54</v>
       </c>
-      <c r="W15" s="23">
+      <c r="W15" s="27">
         <v>30</v>
       </c>
-      <c r="X15" s="23">
+      <c r="X15" s="27">
         <v>10</v>
       </c>
-      <c r="Y15" s="24">
+      <c r="Y15" s="28">
         <v>3.3290118569999998</v>
       </c>
-      <c r="Z15" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="24">
+      <c r="Z15" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="28">
         <v>1.6760588059999999</v>
       </c>
-      <c r="AB15" s="24">
+      <c r="AB15" s="28">
         <v>5.08585537</v>
       </c>
-      <c r="AC15" s="24">
+      <c r="AC15" s="28">
         <v>1.1878024650000001</v>
       </c>
-      <c r="AD15" s="24">
+      <c r="AD15" s="28">
         <v>9.6663467290000007</v>
       </c>
-      <c r="AE15" s="24">
+      <c r="AE15" s="28">
         <v>0.89792168000000006</v>
       </c>
-      <c r="AF15" s="24">
+      <c r="AF15" s="28">
         <v>10.94427514</v>
       </c>
-      <c r="AG15" s="24">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="24">
+      <c r="AG15" s="28">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="28">
         <v>13.11528579</v>
       </c>
     </row>
@@ -18436,851 +18448,851 @@
         <v>8.2191780820000009</v>
       </c>
     </row>
-    <row r="140" spans="1:34" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="23" t="s">
+    <row r="140" spans="1:34" s="27" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="B140" s="23">
+      <c r="B140" s="27">
         <v>7000</v>
       </c>
-      <c r="C140" s="23">
+      <c r="C140" s="27">
         <v>47</v>
       </c>
-      <c r="D140" s="23">
+      <c r="D140" s="27">
         <v>20.5</v>
       </c>
-      <c r="E140" s="23">
+      <c r="E140" s="27">
         <v>15</v>
       </c>
-      <c r="F140" s="23">
+      <c r="F140" s="27">
         <v>10.15</v>
       </c>
-      <c r="G140" s="23">
+      <c r="G140" s="27">
         <v>5</v>
       </c>
-      <c r="H140" s="23">
+      <c r="H140" s="27">
         <v>0.5</v>
       </c>
-      <c r="I140" s="23">
+      <c r="I140" s="27">
         <v>47</v>
       </c>
-      <c r="J140" s="23">
+      <c r="J140" s="27">
         <v>23.99</v>
       </c>
-      <c r="K140" s="23">
+      <c r="K140" s="27">
         <v>12.513999999999999</v>
       </c>
-      <c r="L140" s="23">
+      <c r="L140" s="27">
         <f t="shared" si="6"/>
         <v>9.1521602220622995</v>
       </c>
-      <c r="M140" s="23">
+      <c r="M140" s="27">
         <v>18.66</v>
       </c>
-      <c r="N140" s="23">
+      <c r="N140" s="27">
         <f t="shared" si="7"/>
         <v>7.5867304236309812</v>
       </c>
-      <c r="O140" s="23">
+      <c r="O140" s="27">
         <v>-1.65</v>
       </c>
-      <c r="P140" s="23">
-        <v>0</v>
-      </c>
-      <c r="Q140" s="23">
+      <c r="P140" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q140" s="27">
         <v>1</v>
       </c>
-      <c r="R140" s="23">
+      <c r="R140" s="27">
         <v>0.5</v>
       </c>
-      <c r="S140" s="23">
+      <c r="S140" s="27">
         <v>0.05</v>
       </c>
-      <c r="T140" s="23">
+      <c r="T140" s="27">
         <v>0.05</v>
       </c>
-      <c r="U140" s="23">
+      <c r="U140" s="27">
         <v>0.5</v>
       </c>
-      <c r="V140" s="23">
+      <c r="V140" s="27">
         <v>0.5</v>
       </c>
-      <c r="W140" s="23">
+      <c r="W140" s="27">
         <v>52</v>
       </c>
-      <c r="X140" s="23">
+      <c r="X140" s="27">
         <v>10</v>
       </c>
-      <c r="Y140" s="24">
+      <c r="Y140" s="28">
         <v>9.9450000000000003</v>
       </c>
-      <c r="Z140" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA140" s="24">
+      <c r="Z140" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA140" s="28">
         <v>4.05</v>
       </c>
-      <c r="AB140" s="24">
+      <c r="AB140" s="28">
         <v>7.99</v>
       </c>
-      <c r="AC140" s="24">
+      <c r="AC140" s="28">
         <v>3.2130000000000001</v>
       </c>
-      <c r="AD140" s="24">
+      <c r="AD140" s="28">
         <v>11.99</v>
       </c>
-      <c r="AE140" s="24">
+      <c r="AE140" s="28">
         <v>2.63</v>
       </c>
-      <c r="AF140" s="24">
+      <c r="AF140" s="28">
         <v>13.97</v>
       </c>
-      <c r="AG140" s="24">
-        <v>0</v>
-      </c>
-      <c r="AH140" s="24">
+      <c r="AG140" s="28">
+        <v>0</v>
+      </c>
+      <c r="AH140" s="28">
         <v>18</v>
       </c>
     </row>
-    <row r="141" spans="1:34" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="23" t="s">
+    <row r="141" spans="1:34" s="27" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="B141" s="23">
+      <c r="B141" s="27">
         <v>6000</v>
       </c>
-      <c r="C141" s="23">
+      <c r="C141" s="27">
         <v>47</v>
       </c>
-      <c r="D141" s="23">
+      <c r="D141" s="27">
         <v>20.5</v>
       </c>
-      <c r="E141" s="23">
+      <c r="E141" s="27">
         <v>15</v>
       </c>
-      <c r="F141" s="23">
+      <c r="F141" s="27">
         <v>10.15</v>
       </c>
-      <c r="G141" s="23">
+      <c r="G141" s="27">
         <v>5</v>
       </c>
-      <c r="H141" s="23">
+      <c r="H141" s="27">
         <v>0.5</v>
       </c>
-      <c r="I141" s="23">
+      <c r="I141" s="27">
         <v>47</v>
       </c>
-      <c r="J141" s="23">
+      <c r="J141" s="27">
         <v>23.99</v>
       </c>
-      <c r="K141" s="23">
+      <c r="K141" s="27">
         <v>12.513999999999999</v>
       </c>
-      <c r="L141" s="23">
+      <c r="L141" s="27">
         <f t="shared" si="6"/>
         <v>9.1521602220622995</v>
       </c>
-      <c r="M141" s="23">
+      <c r="M141" s="27">
         <v>18.66</v>
       </c>
-      <c r="N141" s="23">
+      <c r="N141" s="27">
         <f t="shared" si="7"/>
         <v>7.5867304236309812</v>
       </c>
-      <c r="O141" s="23">
+      <c r="O141" s="27">
         <v>-1.65</v>
       </c>
-      <c r="P141" s="23">
-        <v>0</v>
-      </c>
-      <c r="Q141" s="23">
+      <c r="P141" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q141" s="27">
         <v>1</v>
       </c>
-      <c r="R141" s="23">
+      <c r="R141" s="27">
         <v>0.5</v>
       </c>
-      <c r="S141" s="23">
+      <c r="S141" s="27">
         <v>0.05</v>
       </c>
-      <c r="T141" s="23">
+      <c r="T141" s="27">
         <v>0.05</v>
       </c>
-      <c r="U141" s="23">
+      <c r="U141" s="27">
         <v>0.5</v>
       </c>
-      <c r="V141" s="23">
+      <c r="V141" s="27">
         <v>0.5</v>
       </c>
-      <c r="W141" s="23">
+      <c r="W141" s="27">
         <v>52</v>
       </c>
-      <c r="X141" s="23">
+      <c r="X141" s="27">
         <v>10</v>
       </c>
-      <c r="Y141" s="24">
+      <c r="Y141" s="28">
         <v>7.3065306120000004</v>
       </c>
-      <c r="Z141" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA141" s="24">
+      <c r="Z141" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA141" s="28">
         <v>2.9755102039999999</v>
       </c>
-      <c r="AB141" s="24">
+      <c r="AB141" s="28">
         <v>6.8485714289999997</v>
       </c>
-      <c r="AC141" s="24">
+      <c r="AC141" s="28">
         <v>2.3605714290000002</v>
       </c>
-      <c r="AD141" s="24">
+      <c r="AD141" s="28">
         <v>10.27714286</v>
       </c>
-      <c r="AE141" s="24">
+      <c r="AE141" s="28">
         <v>1.932244898</v>
       </c>
-      <c r="AF141" s="24">
+      <c r="AF141" s="28">
         <v>11.97428571</v>
       </c>
-      <c r="AG141" s="24">
-        <v>0</v>
-      </c>
-      <c r="AH141" s="24">
+      <c r="AG141" s="28">
+        <v>0</v>
+      </c>
+      <c r="AH141" s="28">
         <v>15.42857143</v>
       </c>
     </row>
-    <row r="142" spans="1:34" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="23" t="s">
+    <row r="142" spans="1:34" s="27" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="27" t="s">
         <v>156</v>
       </c>
-      <c r="B142" s="23">
+      <c r="B142" s="27">
         <v>5000</v>
       </c>
-      <c r="C142" s="23">
+      <c r="C142" s="27">
         <v>47</v>
       </c>
-      <c r="D142" s="23">
+      <c r="D142" s="27">
         <v>20.5</v>
       </c>
-      <c r="E142" s="23">
+      <c r="E142" s="27">
         <v>15</v>
       </c>
-      <c r="F142" s="23">
+      <c r="F142" s="27">
         <v>10.15</v>
       </c>
-      <c r="G142" s="23">
+      <c r="G142" s="27">
         <v>5</v>
       </c>
-      <c r="H142" s="23">
+      <c r="H142" s="27">
         <v>0.5</v>
       </c>
-      <c r="I142" s="23">
+      <c r="I142" s="27">
         <v>47</v>
       </c>
-      <c r="J142" s="23">
+      <c r="J142" s="27">
         <v>23.99</v>
       </c>
-      <c r="K142" s="23">
+      <c r="K142" s="27">
         <v>12.513999999999999</v>
       </c>
-      <c r="L142" s="23">
+      <c r="L142" s="27">
         <f t="shared" si="6"/>
         <v>9.1521602220622995</v>
       </c>
-      <c r="M142" s="23">
+      <c r="M142" s="27">
         <v>18.66</v>
       </c>
-      <c r="N142" s="23">
+      <c r="N142" s="27">
         <f t="shared" si="7"/>
         <v>7.5867304236309812</v>
       </c>
-      <c r="O142" s="23">
+      <c r="O142" s="27">
         <v>-1.65</v>
       </c>
-      <c r="P142" s="23">
-        <v>0</v>
-      </c>
-      <c r="Q142" s="23">
+      <c r="P142" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q142" s="27">
         <v>1</v>
       </c>
-      <c r="R142" s="23">
+      <c r="R142" s="27">
         <v>0.5</v>
       </c>
-      <c r="S142" s="23">
+      <c r="S142" s="27">
         <v>0.05</v>
       </c>
-      <c r="T142" s="23">
+      <c r="T142" s="27">
         <v>0.05</v>
       </c>
-      <c r="U142" s="23">
+      <c r="U142" s="27">
         <v>0.5</v>
       </c>
-      <c r="V142" s="23">
+      <c r="V142" s="27">
         <v>0.5</v>
       </c>
-      <c r="W142" s="23">
+      <c r="W142" s="27">
         <v>52</v>
       </c>
-      <c r="X142" s="23">
+      <c r="X142" s="27">
         <v>10</v>
       </c>
-      <c r="Y142" s="24">
+      <c r="Y142" s="28">
         <v>5.0739795919999997</v>
       </c>
-      <c r="Z142" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA142" s="24">
+      <c r="Z142" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA142" s="28">
         <v>2.0663265310000001</v>
       </c>
-      <c r="AB142" s="24">
+      <c r="AB142" s="28">
         <v>5.707142857</v>
       </c>
-      <c r="AC142" s="24">
+      <c r="AC142" s="28">
         <v>1.6392857139999999</v>
       </c>
-      <c r="AD142" s="24">
+      <c r="AD142" s="28">
         <v>8.5642857140000004</v>
       </c>
-      <c r="AE142" s="24">
+      <c r="AE142" s="28">
         <v>1.341836735</v>
       </c>
-      <c r="AF142" s="24">
+      <c r="AF142" s="28">
         <v>9.9785714290000005</v>
       </c>
-      <c r="AG142" s="24">
-        <v>0</v>
-      </c>
-      <c r="AH142" s="24">
+      <c r="AG142" s="28">
+        <v>0</v>
+      </c>
+      <c r="AH142" s="28">
         <v>12.85714286</v>
       </c>
     </row>
-    <row r="143" spans="1:34" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="23" t="s">
+    <row r="143" spans="1:34" s="27" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A143" s="27" t="s">
         <v>156</v>
       </c>
-      <c r="B143" s="23">
+      <c r="B143" s="27">
         <v>4000</v>
       </c>
-      <c r="C143" s="23">
+      <c r="C143" s="27">
         <v>47</v>
       </c>
-      <c r="D143" s="23">
+      <c r="D143" s="27">
         <v>20.5</v>
       </c>
-      <c r="E143" s="23">
+      <c r="E143" s="27">
         <v>15</v>
       </c>
-      <c r="F143" s="23">
+      <c r="F143" s="27">
         <v>10.15</v>
       </c>
-      <c r="G143" s="23">
+      <c r="G143" s="27">
         <v>5</v>
       </c>
-      <c r="H143" s="23">
+      <c r="H143" s="27">
         <v>0.5</v>
       </c>
-      <c r="I143" s="23">
+      <c r="I143" s="27">
         <v>47</v>
       </c>
-      <c r="J143" s="23">
+      <c r="J143" s="27">
         <v>23.99</v>
       </c>
-      <c r="K143" s="23">
+      <c r="K143" s="27">
         <v>12.513999999999999</v>
       </c>
-      <c r="L143" s="23">
+      <c r="L143" s="27">
         <f t="shared" si="6"/>
         <v>9.1521602220622995</v>
       </c>
-      <c r="M143" s="23">
+      <c r="M143" s="27">
         <v>18.66</v>
       </c>
-      <c r="N143" s="23">
+      <c r="N143" s="27">
         <f t="shared" si="7"/>
         <v>7.5867304236309812</v>
       </c>
-      <c r="O143" s="23">
+      <c r="O143" s="27">
         <v>-1.65</v>
       </c>
-      <c r="P143" s="23">
-        <v>0</v>
-      </c>
-      <c r="Q143" s="23">
+      <c r="P143" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q143" s="27">
         <v>1</v>
       </c>
-      <c r="R143" s="23">
+      <c r="R143" s="27">
         <v>0.5</v>
       </c>
-      <c r="S143" s="23">
+      <c r="S143" s="27">
         <v>0.05</v>
       </c>
-      <c r="T143" s="23">
+      <c r="T143" s="27">
         <v>0.05</v>
       </c>
-      <c r="U143" s="23">
+      <c r="U143" s="27">
         <v>0.5</v>
       </c>
-      <c r="V143" s="23">
+      <c r="V143" s="27">
         <v>0.5</v>
       </c>
-      <c r="W143" s="23">
+      <c r="W143" s="27">
         <v>52</v>
       </c>
-      <c r="X143" s="23">
+      <c r="X143" s="27">
         <v>10</v>
       </c>
-      <c r="Y143" s="24">
+      <c r="Y143" s="28">
         <v>3.2473469389999998</v>
       </c>
-      <c r="Z143" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA143" s="24">
+      <c r="Z143" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA143" s="28">
         <v>1.3224489800000001</v>
       </c>
-      <c r="AB143" s="24">
+      <c r="AB143" s="28">
         <v>4.5657142860000004</v>
       </c>
-      <c r="AC143" s="24">
+      <c r="AC143" s="28">
         <v>1.0491428570000001</v>
       </c>
-      <c r="AD143" s="24">
+      <c r="AD143" s="28">
         <v>6.8514285709999996</v>
       </c>
-      <c r="AE143" s="24">
+      <c r="AE143" s="28">
         <v>0.85877550999999996</v>
       </c>
-      <c r="AF143" s="24">
+      <c r="AF143" s="28">
         <v>7.9828571430000004</v>
       </c>
-      <c r="AG143" s="24">
-        <v>0</v>
-      </c>
-      <c r="AH143" s="24">
+      <c r="AG143" s="28">
+        <v>0</v>
+      </c>
+      <c r="AH143" s="28">
         <v>10.28571429</v>
       </c>
     </row>
-    <row r="144" spans="1:34" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="23" t="s">
+    <row r="144" spans="1:34" s="27" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A144" s="27" t="s">
         <v>157</v>
       </c>
-      <c r="B144" s="23">
+      <c r="B144" s="27">
         <v>7000</v>
       </c>
-      <c r="C144" s="23">
+      <c r="C144" s="27">
         <v>47</v>
       </c>
-      <c r="D144" s="23">
+      <c r="D144" s="27">
         <v>20.5</v>
       </c>
-      <c r="E144" s="23">
+      <c r="E144" s="27">
         <v>15</v>
       </c>
-      <c r="F144" s="23">
+      <c r="F144" s="27">
         <v>10.15</v>
       </c>
-      <c r="G144" s="23">
+      <c r="G144" s="27">
         <v>7</v>
       </c>
-      <c r="H144" s="23">
+      <c r="H144" s="27">
         <v>0.5</v>
       </c>
-      <c r="I144" s="23">
+      <c r="I144" s="27">
         <v>49.720999999999997</v>
       </c>
-      <c r="J144" s="23">
+      <c r="J144" s="27">
         <v>26.09</v>
       </c>
-      <c r="K144" s="23">
+      <c r="K144" s="27">
         <v>10.06</v>
       </c>
-      <c r="L144" s="23">
+      <c r="L144" s="27">
         <f t="shared" si="6"/>
         <v>7.6748277133479599</v>
       </c>
-      <c r="M144" s="23">
+      <c r="M144" s="27">
         <v>17.39</v>
       </c>
-      <c r="N144" s="23">
+      <c r="N144" s="27">
         <f t="shared" si="7"/>
         <v>7.6478164190306721</v>
       </c>
-      <c r="O144" s="23">
+      <c r="O144" s="27">
         <v>-1.65</v>
       </c>
-      <c r="P144" s="23">
-        <v>0</v>
-      </c>
-      <c r="Q144" s="23">
+      <c r="P144" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q144" s="27">
         <v>1</v>
       </c>
-      <c r="R144" s="23">
+      <c r="R144" s="27">
         <v>0.5</v>
       </c>
-      <c r="S144" s="23">
+      <c r="S144" s="27">
         <v>0.05</v>
       </c>
-      <c r="T144" s="23">
+      <c r="T144" s="27">
         <v>0.05</v>
       </c>
-      <c r="U144" s="23">
+      <c r="U144" s="27">
         <v>0.5</v>
       </c>
-      <c r="V144" s="23">
+      <c r="V144" s="27">
         <v>0.5</v>
       </c>
-      <c r="W144" s="23">
+      <c r="W144" s="27">
         <v>52</v>
       </c>
-      <c r="X144" s="23">
+      <c r="X144" s="27">
         <v>10</v>
       </c>
-      <c r="Y144" s="24">
+      <c r="Y144" s="28">
         <v>10.08</v>
       </c>
-      <c r="Z144" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA144" s="24">
+      <c r="Z144" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA144" s="28">
         <v>3.25</v>
       </c>
-      <c r="AB144" s="24">
+      <c r="AB144" s="28">
         <v>10.08</v>
       </c>
-      <c r="AC144" s="24">
+      <c r="AC144" s="28">
         <v>3.3639999999999999</v>
       </c>
-      <c r="AD144" s="24">
+      <c r="AD144" s="28">
         <v>11.98</v>
       </c>
-      <c r="AE144" s="24">
+      <c r="AE144" s="28">
         <v>3.38</v>
       </c>
-      <c r="AF144" s="24">
+      <c r="AF144" s="28">
         <v>13.99</v>
       </c>
-      <c r="AG144" s="24">
-        <v>0</v>
-      </c>
-      <c r="AH144" s="24">
+      <c r="AG144" s="28">
+        <v>0</v>
+      </c>
+      <c r="AH144" s="28">
         <v>19.5</v>
       </c>
     </row>
-    <row r="145" spans="1:34" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="23" t="s">
+    <row r="145" spans="1:34" s="27" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A145" s="27" t="s">
         <v>157</v>
       </c>
-      <c r="B145" s="23">
+      <c r="B145" s="27">
         <v>6000</v>
       </c>
-      <c r="C145" s="23">
+      <c r="C145" s="27">
         <v>47</v>
       </c>
-      <c r="D145" s="23">
+      <c r="D145" s="27">
         <v>20.5</v>
       </c>
-      <c r="E145" s="23">
+      <c r="E145" s="27">
         <v>15</v>
       </c>
-      <c r="F145" s="23">
+      <c r="F145" s="27">
         <v>10.15</v>
       </c>
-      <c r="G145" s="23">
+      <c r="G145" s="27">
         <v>7</v>
       </c>
-      <c r="H145" s="23">
+      <c r="H145" s="27">
         <v>0.5</v>
       </c>
-      <c r="I145" s="23">
+      <c r="I145" s="27">
         <v>49.720999999999997</v>
       </c>
-      <c r="J145" s="23">
+      <c r="J145" s="27">
         <v>26.09</v>
       </c>
-      <c r="K145" s="23">
+      <c r="K145" s="27">
         <v>10.06</v>
       </c>
-      <c r="L145" s="23">
+      <c r="L145" s="27">
         <f t="shared" si="6"/>
         <v>7.6748277133479599</v>
       </c>
-      <c r="M145" s="23">
+      <c r="M145" s="27">
         <v>17.39</v>
       </c>
-      <c r="N145" s="23">
+      <c r="N145" s="27">
         <f t="shared" si="7"/>
         <v>7.6478164190306721</v>
       </c>
-      <c r="O145" s="23">
+      <c r="O145" s="27">
         <v>-1.65</v>
       </c>
-      <c r="P145" s="23">
-        <v>0</v>
-      </c>
-      <c r="Q145" s="23">
+      <c r="P145" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q145" s="27">
         <v>1</v>
       </c>
-      <c r="R145" s="23">
+      <c r="R145" s="27">
         <v>0.5</v>
       </c>
-      <c r="S145" s="23">
+      <c r="S145" s="27">
         <v>0.05</v>
       </c>
-      <c r="T145" s="23">
+      <c r="T145" s="27">
         <v>0.05</v>
       </c>
-      <c r="U145" s="23">
+      <c r="U145" s="27">
         <v>0.5</v>
       </c>
-      <c r="V145" s="23">
+      <c r="V145" s="27">
         <v>0.5</v>
       </c>
-      <c r="W145" s="23">
+      <c r="W145" s="27">
         <v>52</v>
       </c>
-      <c r="X145" s="23">
+      <c r="X145" s="27">
         <v>10</v>
       </c>
-      <c r="Y145" s="24">
+      <c r="Y145" s="28">
         <v>7.4057142860000003</v>
       </c>
-      <c r="Z145" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA145" s="24">
+      <c r="Z145" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA145" s="28">
         <v>2.3877551019999999</v>
       </c>
-      <c r="AB145" s="24">
+      <c r="AB145" s="28">
         <v>8.64</v>
       </c>
-      <c r="AC145" s="24">
+      <c r="AC145" s="28">
         <v>2.4715102039999999</v>
       </c>
-      <c r="AD145" s="24">
+      <c r="AD145" s="28">
         <v>10.26857143</v>
       </c>
-      <c r="AE145" s="24">
+      <c r="AE145" s="28">
         <v>2.4832653059999998</v>
       </c>
-      <c r="AF145" s="24">
+      <c r="AF145" s="28">
         <v>11.99142857</v>
       </c>
-      <c r="AG145" s="24">
-        <v>0</v>
-      </c>
-      <c r="AH145" s="24">
+      <c r="AG145" s="28">
+        <v>0</v>
+      </c>
+      <c r="AH145" s="28">
         <v>16.714285709999999</v>
       </c>
     </row>
-    <row r="146" spans="1:34" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="23" t="s">
+    <row r="146" spans="1:34" s="27" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="27" t="s">
         <v>158</v>
       </c>
-      <c r="B146" s="23">
+      <c r="B146" s="27">
         <v>5000</v>
       </c>
-      <c r="C146" s="23">
+      <c r="C146" s="27">
         <v>47</v>
       </c>
-      <c r="D146" s="23">
+      <c r="D146" s="27">
         <v>20.5</v>
       </c>
-      <c r="E146" s="23">
+      <c r="E146" s="27">
         <v>15</v>
       </c>
-      <c r="F146" s="23">
+      <c r="F146" s="27">
         <v>10.15</v>
       </c>
-      <c r="G146" s="23">
+      <c r="G146" s="27">
         <v>7</v>
       </c>
-      <c r="H146" s="23">
+      <c r="H146" s="27">
         <v>0.5</v>
       </c>
-      <c r="I146" s="23">
+      <c r="I146" s="27">
         <v>49.720999999999997</v>
       </c>
-      <c r="J146" s="23">
+      <c r="J146" s="27">
         <v>26.09</v>
       </c>
-      <c r="K146" s="23">
+      <c r="K146" s="27">
         <v>10.06</v>
       </c>
-      <c r="L146" s="23">
+      <c r="L146" s="27">
         <f t="shared" si="6"/>
         <v>7.6748277133479599</v>
       </c>
-      <c r="M146" s="23">
+      <c r="M146" s="27">
         <v>17.39</v>
       </c>
-      <c r="N146" s="23">
+      <c r="N146" s="27">
         <f t="shared" si="7"/>
         <v>7.6478164190306721</v>
       </c>
-      <c r="O146" s="23">
+      <c r="O146" s="27">
         <v>-1.65</v>
       </c>
-      <c r="P146" s="23">
-        <v>0</v>
-      </c>
-      <c r="Q146" s="23">
+      <c r="P146" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q146" s="27">
         <v>1</v>
       </c>
-      <c r="R146" s="23">
+      <c r="R146" s="27">
         <v>0.5</v>
       </c>
-      <c r="S146" s="23">
+      <c r="S146" s="27">
         <v>0.05</v>
       </c>
-      <c r="T146" s="23">
+      <c r="T146" s="27">
         <v>0.05</v>
       </c>
-      <c r="U146" s="23">
+      <c r="U146" s="27">
         <v>0.5</v>
       </c>
-      <c r="V146" s="23">
+      <c r="V146" s="27">
         <v>0.5</v>
       </c>
-      <c r="W146" s="23">
+      <c r="W146" s="27">
         <v>52</v>
       </c>
-      <c r="X146" s="23">
+      <c r="X146" s="27">
         <v>10</v>
       </c>
-      <c r="Y146" s="24">
+      <c r="Y146" s="28">
         <v>5.1428571429999996</v>
       </c>
-      <c r="Z146" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA146" s="24">
+      <c r="Z146" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA146" s="28">
         <v>1.658163265</v>
       </c>
-      <c r="AB146" s="24">
+      <c r="AB146" s="28">
         <v>7.2</v>
       </c>
-      <c r="AC146" s="24">
+      <c r="AC146" s="28">
         <v>1.716326531</v>
       </c>
-      <c r="AD146" s="24">
+      <c r="AD146" s="28">
         <v>8.5571428570000005</v>
       </c>
-      <c r="AE146" s="24">
+      <c r="AE146" s="28">
         <v>1.7244897960000001</v>
       </c>
-      <c r="AF146" s="24">
+      <c r="AF146" s="28">
         <v>9.9928571430000002</v>
       </c>
-      <c r="AG146" s="24">
-        <v>0</v>
-      </c>
-      <c r="AH146" s="24">
+      <c r="AG146" s="28">
+        <v>0</v>
+      </c>
+      <c r="AH146" s="28">
         <v>13.92857143</v>
       </c>
     </row>
-    <row r="147" spans="1:34" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="23" t="s">
+    <row r="147" spans="1:34" s="27" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A147" s="27" t="s">
         <v>158</v>
       </c>
-      <c r="B147" s="23">
+      <c r="B147" s="27">
         <v>4000</v>
       </c>
-      <c r="C147" s="23">
+      <c r="C147" s="27">
         <v>47</v>
       </c>
-      <c r="D147" s="23">
+      <c r="D147" s="27">
         <v>20.5</v>
       </c>
-      <c r="E147" s="23">
+      <c r="E147" s="27">
         <v>15</v>
       </c>
-      <c r="F147" s="23">
+      <c r="F147" s="27">
         <v>10.15</v>
       </c>
-      <c r="G147" s="23">
+      <c r="G147" s="27">
         <v>7</v>
       </c>
-      <c r="H147" s="23">
+      <c r="H147" s="27">
         <v>0.5</v>
       </c>
-      <c r="I147" s="23">
+      <c r="I147" s="27">
         <v>49.720999999999997</v>
       </c>
-      <c r="J147" s="23">
+      <c r="J147" s="27">
         <v>26.09</v>
       </c>
-      <c r="K147" s="23">
+      <c r="K147" s="27">
         <v>10.06</v>
       </c>
-      <c r="L147" s="23">
+      <c r="L147" s="27">
         <f t="shared" si="6"/>
         <v>7.6748277133479599</v>
       </c>
-      <c r="M147" s="23">
+      <c r="M147" s="27">
         <v>17.39</v>
       </c>
-      <c r="N147" s="23">
+      <c r="N147" s="27">
         <f t="shared" si="7"/>
         <v>7.6478164190306721</v>
       </c>
-      <c r="O147" s="23">
+      <c r="O147" s="27">
         <v>-1.65</v>
       </c>
-      <c r="P147" s="23">
-        <v>0</v>
-      </c>
-      <c r="Q147" s="23">
+      <c r="P147" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q147" s="27">
         <v>1</v>
       </c>
-      <c r="R147" s="23">
+      <c r="R147" s="27">
         <v>0.5</v>
       </c>
-      <c r="S147" s="23">
+      <c r="S147" s="27">
         <v>0.05</v>
       </c>
-      <c r="T147" s="23">
+      <c r="T147" s="27">
         <v>0.05</v>
       </c>
-      <c r="U147" s="23">
+      <c r="U147" s="27">
         <v>0.5</v>
       </c>
-      <c r="V147" s="23">
+      <c r="V147" s="27">
         <v>0.5</v>
       </c>
-      <c r="W147" s="23">
+      <c r="W147" s="27">
         <v>52</v>
       </c>
-      <c r="X147" s="23">
+      <c r="X147" s="27">
         <v>10</v>
       </c>
-      <c r="Y147" s="24">
+      <c r="Y147" s="28">
         <v>3.291428571</v>
       </c>
-      <c r="Z147" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA147" s="24">
+      <c r="Z147" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA147" s="28">
         <v>1.0612244900000001</v>
       </c>
-      <c r="AB147" s="24">
+      <c r="AB147" s="28">
         <v>5.76</v>
       </c>
-      <c r="AC147" s="24">
+      <c r="AC147" s="28">
         <v>1.0984489799999999</v>
       </c>
-      <c r="AD147" s="24">
+      <c r="AD147" s="28">
         <v>6.8457142859999998</v>
       </c>
-      <c r="AE147" s="24">
+      <c r="AE147" s="28">
         <v>1.1036734690000001</v>
       </c>
-      <c r="AF147" s="24">
+      <c r="AF147" s="28">
         <v>7.9942857140000001</v>
       </c>
-      <c r="AG147" s="24">
-        <v>0</v>
-      </c>
-      <c r="AH147" s="24">
+      <c r="AG147" s="28">
+        <v>0</v>
+      </c>
+      <c r="AH147" s="28">
         <v>11.14285714</v>
       </c>
     </row>
@@ -23951,16 +23963,16 @@
   </sheetData>
   <autoFilter ref="A3:AH191" xr:uid="{BB97FB68-20BF-40DF-800A-E711A74AB745}"/>
   <mergeCells count="10">
+    <mergeCell ref="Y2:Z2"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="AE2:AF2"/>
+    <mergeCell ref="AG2:AH2"/>
     <mergeCell ref="Y1:Z1"/>
     <mergeCell ref="AA1:AB1"/>
     <mergeCell ref="AC1:AD1"/>
     <mergeCell ref="AE1:AF1"/>
     <mergeCell ref="AG1:AH1"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="AE2:AF2"/>
-    <mergeCell ref="AG2:AH2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
